--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BHNVFEAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\PA\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A21AF18-E41A-4B31-8D96-6A3A3B048707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39088AAB-D03A-4933-A340-B8C28C6C5634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="555" windowWidth="19605" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="100">
   <si>
     <t>Sources:</t>
   </si>
@@ -380,19 +380,21 @@
   <si>
     <t>energy consumption that more closely matches EIA's AEO trajectory: freight LDVs, passenger HDVs, freight HDVs, passenger ships, passenger motorbikes.</t>
   </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="###0.00_)"/>
     <numFmt numFmtId="165" formatCode="#,##0_)"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -1294,7 +1296,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1327,8 +1329,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="154" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="155" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="155" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -1336,6 +1336,9 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="43" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="154" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="155" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4712,169 +4715,169 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>4.236427364823752E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>4.2882977835183994E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>4.3401682022130295E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>4.3920386209076769E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>4.4439090396023069E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>4.4957794582969543E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>4.5476498769915844E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>4.5995202956862317E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>4.6513907143808618E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>4.7032611330755092E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>4.7551315517701392E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>4.8070019704647866E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>4.8588723891594167E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>4.9107428078540641E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>4.9626132265486941E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>5.0144836452433242E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>5.0663540639379716E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>5.1182244826326016E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>5.170094901327249E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>5.2219653200218791E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>5.2738357387165265E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>5.3257061574111565E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>5.3775765761058039E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>5.429446994800434E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>5.4813174134950814E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
                   <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>5.6525537747016295E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>5.6816948983254214E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>5.7128317518608321E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>5.7537137435165198E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>5.8053804811384778E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>5.8402553055494823E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>5.8760417107298871E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>5.9096130220580865E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>5.946019196444121E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>5.9865845018156332E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>6.0321943227520944E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>6.0839429137508894E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>6.1395089969970801E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>6.1977379967962927E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>6.2567088851316315E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>6.3167004143386532E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>6.3779136032516399E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>6.437466870978497E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>6.4981143154692399E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>6.5593323238593052E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>6.6206558943440969E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>6.6830617483670774E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>6.7444724581067943E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>6.8055623616867665E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>6.8655076394605308E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>6.9253674881163997E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>6.9843365885812099E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>7.0421403083949718E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>7.0992567085904998E-4</c:v>
+                  <c:v>5.7245968727451246E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5704,199 +5707,199 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="3" formatCode="0.00E+00">
-                  <c:v>5.6550914138770239E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="0.00E+00">
-                  <c:v>5.5917423769000218E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="0.00E+00">
-                  <c:v>5.5283933399230198E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0.00E+00">
-                  <c:v>5.4650443029460177E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="0.00E+00">
-                  <c:v>5.401695265969033E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="0.00E+00">
-                  <c:v>5.338346228992031E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0.00E+00">
-                  <c:v>5.2749971920150289E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="0.00E+00">
-                  <c:v>5.2116481550380268E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="0.00E+00">
-                  <c:v>5.1482991180610421E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.00E+00">
-                  <c:v>5.0849500810840401E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="0.00E+00">
-                  <c:v>5.021601044107038E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="0.00E+00">
-                  <c:v>4.9582520071300533E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="0.00E+00">
-                  <c:v>4.8949029701530512E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="0.00E+00">
-                  <c:v>4.8315539331760492E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="0.00E+00">
-                  <c:v>4.7682048961990471E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="0.00E+00">
-                  <c:v>4.7048558592220624E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="0.00E+00">
-                  <c:v>4.6415068222450603E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="0.00E+00">
-                  <c:v>4.5781577852680583E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="0.00E+00">
-                  <c:v>4.5148087482910562E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="0.00E+00">
-                  <c:v>4.4514597113140715E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="0.00E+00">
-                  <c:v>4.3881106743370694E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="0.00E+00">
-                  <c:v>4.3247616373600674E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="0.00E+00">
-                  <c:v>4.2614126003830653E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00E+00">
-                  <c:v>4.1980635634060806E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00E+00">
-                  <c:v>4.1347145264290786E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00E+00">
-                  <c:v>4.0713654894520765E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00E+00">
-                  <c:v>4.0080164524750744E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.00E+00">
-                  <c:v>3.9446674154980897E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.00E+00">
-                  <c:v>3.8813183785210877E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.00E+00">
-                  <c:v>3.8179693415440856E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.00E+00">
-                  <c:v>3.7546203045671009E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.00E+00">
-                  <c:v>3.6912712675900988E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.00E+00">
-                  <c:v>3.6279222306130968E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.00E+00">
-                  <c:v>3.5645731936360947E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.00E+00">
-                  <c:v>3.50122415665911E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.00E+00">
-                  <c:v>3.8258341226368855E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.00E+00">
-                  <c:v>3.0425177990638558E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.00E+00">
-                  <c:v>3.1369602145278982E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.00E+00">
-                  <c:v>3.1866725580745358E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.00E+00">
-                  <c:v>3.2176784865192677E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.00E+00">
-                  <c:v>3.2673519826153288E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.00E+00">
-                  <c:v>3.3038240919707824E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.00E+00">
-                  <c:v>3.3340389823551702E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.00E+00">
-                  <c:v>3.3475402773417714E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.00E+00">
-                  <c:v>3.3555107094994109E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.00E+00">
-                  <c:v>3.3533649804280095E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.00E+00">
-                  <c:v>3.3530916094466514E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.00E+00">
-                  <c:v>3.3543094523282268E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.00E+00">
-                  <c:v>3.3562165718775656E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.00E+00">
-                  <c:v>3.3577393040427292E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.00E+00">
-                  <c:v>3.3592389782957394E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.00E+00">
-                  <c:v>3.3615828155893885E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.00E+00">
-                  <c:v>3.3637923107499002E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.00E+00">
-                  <c:v>3.3656727929620473E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.00E+00">
-                  <c:v>3.3676884833871952E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.00E+00">
-                  <c:v>3.3691991114356807E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.00E+00">
-                  <c:v>3.3705013729136348E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.00E+00">
-                  <c:v>3.3713686099786852E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.00E+00">
-                  <c:v>3.3722694633495147E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.00E+00">
-                  <c:v>3.3729739602263772E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.00E+00">
-                  <c:v>3.3742953237129352E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.00E+00">
-                  <c:v>3.3751721202413692E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.00E+00">
-                  <c:v>3.3760101841942016E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.00E+00">
-                  <c:v>3.3764787130259203E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.00E+00">
-                  <c:v>3.3772719520374359E-4</c:v>
+                  <c:v>7.1745362435245036E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7786,19 +7789,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="107.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="31">
+        <v>45321</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -7806,58 +7815,58 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="B4" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="B7" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="B8" s="5">
         <v>2008</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3">
       <c r="B9" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3">
       <c r="B10" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3">
       <c r="B11" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:3">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3">
       <c r="B14" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -9113,99 +9122,99 @@
       </c>
       <c r="B2" s="4">
         <f>B$5/(1-'Other Values'!$B$3)</f>
-        <v>1.3780336177922486E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="C2" s="4">
         <f>C$5/(1-'Other Values'!$B$3)</f>
-        <v>1.394702045298585E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="D2" s="4">
         <f>D$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4113704728049271E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="E2" s="4">
         <f>E$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4280389003112637E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="F2" s="4">
         <f>F$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4447073278176057E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="G2" s="4">
         <f>G$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4613757553239421E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="H2" s="4">
         <f>H$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4780441828302841E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="I2" s="4">
         <f>I$5/(1-'Other Values'!$B$3)</f>
-        <v>1.4947126103366205E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="J2" s="4">
         <f>J$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5113810378429625E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="K2" s="4">
         <f>K$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5280494653492991E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="L2" s="4">
         <f>L$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5447178928556411E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="M2" s="4">
         <f>M$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5613863203619775E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="N2" s="4">
         <f>N$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5780547478683195E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="O2" s="4">
         <f>O$5/(1-'Other Values'!$B$3)</f>
-        <v>1.5947231753746559E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="P2" s="4">
         <f>P$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6113916028809925E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="Q2" s="4">
         <f>Q$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6280600303873345E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="R2" s="4">
         <f>R$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6447284578936709E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="S2" s="4">
         <f>S$5/(1-'Other Values'!$B$3)</f>
-        <v>1.661396885400013E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="T2" s="4">
         <f>T$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6780653129063493E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="U2" s="4">
         <f>U$5/(1-'Other Values'!$B$3)</f>
-        <v>1.6947337404126914E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="V2" s="4">
         <f>V$5/(1-'Other Values'!$B$3)</f>
-        <v>1.711402167919028E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="W2" s="4">
         <f>W$5/(1-'Other Values'!$B$3)</f>
-        <v>1.72807059542537E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="X2" s="4">
         <f>X$5/(1-'Other Values'!$B$3)</f>
-        <v>1.7447390229317064E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="Y2" s="4">
         <f>Y$5/(1-'Other Values'!$B$3)</f>
-        <v>1.7614074504380484E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="Z2" s="4">
         <f>Z$5/(1-'Other Values'!$B$3)</f>
@@ -9213,23 +9222,23 @@
       </c>
       <c r="AA2" s="4">
         <f>AA$5/(1-'Other Values'!$B$3)</f>
-        <v>1.8164338208636196E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="AB2" s="4">
         <f>AB$5/(1-'Other Values'!$B$3)</f>
-        <v>1.8257982470394711E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="AC2" s="4">
         <f>AC$5/(1-'Other Values'!$B$3)</f>
-        <v>1.8358039959613347E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="AD2" s="4">
         <f>AD$5/(1-'Other Values'!$B$3)</f>
-        <v>1.8489413203048922E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="AE2" s="4">
         <f>AE$5/(1-'Other Values'!$B$3)</f>
-        <v>1.865544295415052E-3</v>
+        <v>1.8395846877216544E-3</v>
       </c>
       <c r="AG2" s="4"/>
       <c r="AH2" s="4"/>
@@ -9430,99 +9439,99 @@
       </c>
       <c r="B5" s="4">
         <f>Extrapolations!Q6</f>
-        <v>4.2882977835183994E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="C5" s="4">
         <f>Extrapolations!R6</f>
-        <v>4.3401682022130295E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="D5" s="4">
         <f>Extrapolations!S6</f>
-        <v>4.3920386209076769E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="E5" s="4">
         <f>Extrapolations!T6</f>
-        <v>4.4439090396023069E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="F5" s="4">
         <f>Extrapolations!U6</f>
-        <v>4.4957794582969543E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="G5" s="4">
         <f>Extrapolations!V6</f>
-        <v>4.5476498769915844E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="H5" s="4">
         <f>Extrapolations!W6</f>
-        <v>4.5995202956862317E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="I5" s="4">
         <f>Extrapolations!X6</f>
-        <v>4.6513907143808618E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="J5" s="4">
         <f>Extrapolations!Y6</f>
-        <v>4.7032611330755092E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="K5" s="4">
         <f>Extrapolations!Z6</f>
-        <v>4.7551315517701392E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="L5" s="4">
         <f>Extrapolations!AA6</f>
-        <v>4.8070019704647866E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="M5" s="4">
         <f>Extrapolations!AB6</f>
-        <v>4.8588723891594167E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="N5" s="4">
         <f>Extrapolations!AC6</f>
-        <v>4.9107428078540641E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="O5" s="4">
         <f>Extrapolations!AD6</f>
-        <v>4.9626132265486941E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="P5" s="4">
         <f>Extrapolations!AE6</f>
-        <v>5.0144836452433242E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Q5" s="4">
         <f>Extrapolations!AF6</f>
-        <v>5.0663540639379716E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="R5" s="4">
         <f>Extrapolations!AG6</f>
-        <v>5.1182244826326016E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="S5" s="4">
         <f>Extrapolations!AH6</f>
-        <v>5.170094901327249E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="T5" s="4">
         <f>Extrapolations!AI6</f>
-        <v>5.2219653200218791E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="U5" s="4">
         <f>Extrapolations!AJ6</f>
-        <v>5.2738357387165265E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="V5" s="4">
         <f>Extrapolations!AK6</f>
-        <v>5.3257061574111565E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="W5" s="4">
         <f>Extrapolations!AL6</f>
-        <v>5.3775765761058039E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="X5" s="4">
         <f>Extrapolations!AM6</f>
-        <v>5.429446994800434E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Y5" s="4">
         <f>Extrapolations!AN6</f>
-        <v>5.4813174134950814E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Z5" s="4">
         <f>Extrapolations!AO6</f>
@@ -9530,23 +9539,23 @@
       </c>
       <c r="AA5" s="4">
         <f>Extrapolations!AP6</f>
-        <v>5.6525537747016295E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AB5" s="4">
         <f>Extrapolations!AQ6</f>
-        <v>5.6816948983254214E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AC5" s="4">
         <f>Extrapolations!AR6</f>
-        <v>5.7128317518608321E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AD5" s="4">
         <f>Extrapolations!AS6</f>
-        <v>5.7537137435165198E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AE5" s="4">
         <f>Extrapolations!AT6</f>
-        <v>5.8053804811384778E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
@@ -9747,99 +9756,99 @@
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>1.2864893350555196E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>1.3020504606639086E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>1.3176115862723028E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>1.3331727118806919E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>1.3487338374890861E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>1.3642949630974751E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>1.3798560887058693E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>1.3954172143142583E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>1.4109783399226525E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>1.4265394655310416E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>1.4421005911394358E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>1.4576617167478248E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>1.473222842356219E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>1.488783967964608E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>1.504345093572997E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>1.5199062191813913E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>1.5354673447897803E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>1.5510284703981745E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>1.5665895960065635E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>1.5821507216149577E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>1.5977118472233467E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>1.613272972831741E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>1.62883409844013E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>1.6443952240485242E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
@@ -9847,23 +9856,23 @@
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>1.6957661324104886E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>1.7045084694976261E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>1.7138495255582494E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>1.7261141230549557E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>1.7416141443415431E-3</v>
+        <v>1.7173790618235372E-3</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -10750,7 +10759,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -10758,7 +10767,7 @@
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="30">
+    <row r="1" spans="1:32" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -10853,134 +10862,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
-      <c r="A2" t="s">
+    <row r="2" spans="1:32" s="4" customFormat="1">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4">
         <f>Extrapolations!G9</f>
-        <v>1.7968922323952086E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="C2" s="4">
         <f>Extrapolations!H9</f>
-        <v>1.7765351800131182E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="D2" s="4">
         <f>Extrapolations!I9</f>
-        <v>1.7561781276310348E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="E2" s="4">
         <f>Extrapolations!J9</f>
-        <v>1.7358210752489514E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="F2" s="4">
         <f>Extrapolations!K9</f>
-        <v>1.7154640228668611E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="G2" s="4">
         <f>Extrapolations!L9</f>
-        <v>1.6951069704847777E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="H2" s="4">
         <f>Extrapolations!M9</f>
-        <v>1.6747499181026873E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="I2" s="4">
         <f>Extrapolations!N9</f>
-        <v>1.6543928657206039E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="J2" s="4">
         <f>Extrapolations!O9</f>
-        <v>1.6340358133385205E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="K2" s="4">
         <f>Extrapolations!P9</f>
-        <v>1.6136787609564301E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="L2" s="4">
         <f>Extrapolations!Q9</f>
-        <v>1.5933217085743467E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="M2" s="4">
         <f>Extrapolations!R9</f>
-        <v>1.5729646561922633E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="N2" s="4">
         <f>Extrapolations!S9</f>
-        <v>1.552607603810173E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="O2" s="4">
         <f>Extrapolations!T9</f>
-        <v>1.5322505514280896E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="P2" s="4">
         <f>Extrapolations!U9</f>
-        <v>1.5118934990460062E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Q2" s="4">
         <f>Extrapolations!V9</f>
-        <v>1.4915364466639158E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="R2" s="4">
         <f>Extrapolations!W9</f>
-        <v>1.4711793942818324E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="S2" s="4">
         <f>Extrapolations!X9</f>
-        <v>1.450822341899749E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="T2" s="4">
         <f>Extrapolations!Y9</f>
-        <v>1.4304652895176587E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="U2" s="4">
         <f>Extrapolations!Z9</f>
-        <v>1.4101082371355753E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="V2" s="4">
         <f>Extrapolations!AA9</f>
-        <v>1.3897511847534849E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="W2" s="4">
         <f>Extrapolations!AB9</f>
-        <v>1.3693941323714015E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="X2" s="4">
         <f>Extrapolations!AC9</f>
-        <v>1.3490370799893181E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Y2" s="4">
         <f>Extrapolations!AD9</f>
-        <v>1.3286800276072278E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Z2" s="4">
         <f>Extrapolations!AE9</f>
-        <v>1.3083229752251443E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AA2" s="4">
         <f>Extrapolations!AF9</f>
-        <v>1.2879659228430609E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AB2" s="4">
         <f>Extrapolations!AG9</f>
-        <v>1.2676088704609706E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AC2" s="4">
         <f>Extrapolations!AH9</f>
-        <v>1.2472518180788872E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AD2" s="4">
         <f>Extrapolations!AI9</f>
-        <v>1.2268947656968038E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AE2" s="4">
         <f>Extrapolations!AJ9</f>
-        <v>1.2065377133147134E-3</v>
-      </c>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -11075,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -11170,134 +11177,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="22">
-        <f>Extrapolations!Q6</f>
-        <v>4.2882977835183994E-4</v>
-      </c>
-      <c r="C5" s="22">
-        <f>Extrapolations!R6</f>
-        <v>4.3401682022130295E-4</v>
-      </c>
-      <c r="D5" s="22">
-        <f>Extrapolations!S6</f>
-        <v>4.3920386209076769E-4</v>
-      </c>
-      <c r="E5" s="22">
-        <f>Extrapolations!T6</f>
-        <v>4.4439090396023069E-4</v>
-      </c>
-      <c r="F5" s="22">
-        <f>Extrapolations!U6</f>
-        <v>4.4957794582969543E-4</v>
-      </c>
-      <c r="G5" s="22">
-        <f>Extrapolations!V6</f>
-        <v>4.5476498769915844E-4</v>
-      </c>
-      <c r="H5" s="22">
-        <f>Extrapolations!W6</f>
-        <v>4.5995202956862317E-4</v>
-      </c>
-      <c r="I5" s="22">
-        <f>Extrapolations!X6</f>
-        <v>4.6513907143808618E-4</v>
-      </c>
-      <c r="J5" s="22">
-        <f>Extrapolations!Y6</f>
-        <v>4.7032611330755092E-4</v>
-      </c>
-      <c r="K5" s="22">
-        <f>Extrapolations!Z6</f>
-        <v>4.7551315517701392E-4</v>
-      </c>
-      <c r="L5" s="22">
-        <f>Extrapolations!AA6</f>
-        <v>4.8070019704647866E-4</v>
-      </c>
-      <c r="M5" s="22">
-        <f>Extrapolations!AB6</f>
-        <v>4.8588723891594167E-4</v>
-      </c>
-      <c r="N5" s="22">
-        <f>Extrapolations!AC6</f>
-        <v>4.9107428078540641E-4</v>
-      </c>
-      <c r="O5" s="22">
-        <f>Extrapolations!AD6</f>
-        <v>4.9626132265486941E-4</v>
-      </c>
-      <c r="P5" s="22">
-        <f>Extrapolations!AE6</f>
-        <v>5.0144836452433242E-4</v>
-      </c>
-      <c r="Q5" s="22">
-        <f>Extrapolations!AF6</f>
-        <v>5.0663540639379716E-4</v>
-      </c>
-      <c r="R5" s="22">
-        <f>Extrapolations!AG6</f>
-        <v>5.1182244826326016E-4</v>
-      </c>
-      <c r="S5" s="22">
-        <f>Extrapolations!AH6</f>
-        <v>5.170094901327249E-4</v>
-      </c>
-      <c r="T5" s="22">
-        <f>Extrapolations!AI6</f>
-        <v>5.2219653200218791E-4</v>
-      </c>
-      <c r="U5" s="22">
-        <f>Extrapolations!AJ6</f>
-        <v>5.2738357387165265E-4</v>
-      </c>
-      <c r="V5" s="22">
-        <f>Extrapolations!AK6</f>
-        <v>5.3257061574111565E-4</v>
-      </c>
-      <c r="W5" s="22">
-        <f>Extrapolations!AL6</f>
-        <v>5.3775765761058039E-4</v>
-      </c>
-      <c r="X5" s="22">
-        <f>Extrapolations!AM6</f>
-        <v>5.429446994800434E-4</v>
-      </c>
-      <c r="Y5" s="22">
-        <f>Extrapolations!AN6</f>
-        <v>5.4813174134950814E-4</v>
-      </c>
-      <c r="Z5" s="22">
-        <f>Extrapolations!AO6</f>
-        <v>5.7245968727451246E-4</v>
-      </c>
-      <c r="AA5" s="22">
-        <f>Extrapolations!AP6</f>
-        <v>5.6525537747016295E-4</v>
-      </c>
-      <c r="AB5" s="22">
-        <f>Extrapolations!AQ6</f>
-        <v>5.6816948983254214E-4</v>
-      </c>
-      <c r="AC5" s="22">
-        <f>Extrapolations!AR6</f>
-        <v>5.7128317518608321E-4</v>
-      </c>
-      <c r="AD5" s="22">
-        <f>Extrapolations!AS6</f>
-        <v>5.7537137435165198E-4</v>
-      </c>
-      <c r="AE5" s="22">
-        <f>Extrapolations!AT6</f>
-        <v>5.8053804811384778E-4</v>
-      </c>
-      <c r="AG5" s="4"/>
-      <c r="AH5" s="4"/>
+      <c r="B5" s="29">
+        <f>Extrapolations!G8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="C5" s="29">
+        <f>Extrapolations!H8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="D5" s="29">
+        <f>Extrapolations!I8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="E5" s="29">
+        <f>Extrapolations!J8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="F5" s="29">
+        <f>Extrapolations!K8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="G5" s="29">
+        <f>Extrapolations!L8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="H5" s="29">
+        <f>Extrapolations!M8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="I5" s="29">
+        <f>Extrapolations!N8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="J5" s="29">
+        <f>Extrapolations!O8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="K5" s="29">
+        <f>Extrapolations!P8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="L5" s="29">
+        <f>Extrapolations!Q8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="M5" s="29">
+        <f>Extrapolations!R8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="N5" s="29">
+        <f>Extrapolations!S8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="O5" s="29">
+        <f>Extrapolations!T8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="P5" s="29">
+        <f>Extrapolations!U8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="Q5" s="29">
+        <f>Extrapolations!V8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="R5" s="29">
+        <f>Extrapolations!W8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="S5" s="29">
+        <f>Extrapolations!X8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="T5" s="29">
+        <f>Extrapolations!Y8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="U5" s="29">
+        <f>Extrapolations!Z8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="V5" s="29">
+        <f>Extrapolations!AA8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="W5" s="29">
+        <f>Extrapolations!AB8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="X5" s="29">
+        <f>Extrapolations!AC8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="Y5" s="29">
+        <f>Extrapolations!AD8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="Z5" s="29">
+        <f>Extrapolations!AE8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AA5" s="29">
+        <f>Extrapolations!AF8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AB5" s="29">
+        <f>Extrapolations!AG8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AC5" s="29">
+        <f>Extrapolations!AH8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AD5" s="29">
+        <f>Extrapolations!AI8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AE5" s="29">
+        <f>Extrapolations!AJ8</f>
+        <v>7.1745362435245036E-5</v>
+      </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -11392,7 +11397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -11487,165 +11492,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
-      <c r="A8" t="s">
+    <row r="8" spans="1:32" s="4" customFormat="1">
+      <c r="A8" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B8" s="4">
         <f>B$5*Calculations!$B$27</f>
-        <v>1.2864893350555196E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="C8" s="4">
         <f>C$5*Calculations!$B$27</f>
-        <v>1.3020504606639086E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="D8" s="4">
         <f>D$5*Calculations!$B$27</f>
-        <v>1.3176115862723028E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="E8" s="4">
         <f>E$5*Calculations!$B$27</f>
-        <v>1.3331727118806919E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="F8" s="4">
         <f>F$5*Calculations!$B$27</f>
-        <v>1.3487338374890861E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="G8" s="4">
         <f>G$5*Calculations!$B$27</f>
-        <v>1.3642949630974751E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="H8" s="4">
         <f>H$5*Calculations!$B$27</f>
-        <v>1.3798560887058693E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="I8" s="4">
         <f>I$5*Calculations!$B$27</f>
-        <v>1.3954172143142583E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="J8" s="4">
         <f>J$5*Calculations!$B$27</f>
-        <v>1.4109783399226525E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="K8" s="4">
         <f>K$5*Calculations!$B$27</f>
-        <v>1.4265394655310416E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="L8" s="4">
         <f>L$5*Calculations!$B$27</f>
-        <v>1.4421005911394358E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="M8" s="4">
         <f>M$5*Calculations!$B$27</f>
-        <v>1.4576617167478248E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="N8" s="4">
         <f>N$5*Calculations!$B$27</f>
-        <v>1.473222842356219E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="O8" s="4">
         <f>O$5*Calculations!$B$27</f>
-        <v>1.488783967964608E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="P8" s="4">
         <f>P$5*Calculations!$B$27</f>
-        <v>1.504345093572997E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="Q8" s="4">
         <f>Q$5*Calculations!$B$27</f>
-        <v>1.5199062191813913E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="R8" s="4">
         <f>R$5*Calculations!$B$27</f>
-        <v>1.5354673447897803E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="S8" s="4">
         <f>S$5*Calculations!$B$27</f>
-        <v>1.5510284703981745E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="T8" s="4">
         <f>T$5*Calculations!$B$27</f>
-        <v>1.5665895960065635E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="U8" s="4">
         <f>U$5*Calculations!$B$27</f>
-        <v>1.5821507216149577E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="V8" s="4">
         <f>V$5*Calculations!$B$27</f>
-        <v>1.5977118472233467E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="W8" s="4">
         <f>W$5*Calculations!$B$27</f>
-        <v>1.613272972831741E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="X8" s="4">
         <f>X$5*Calculations!$B$27</f>
-        <v>1.62883409844013E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="Y8" s="4">
         <f>Y$5*Calculations!$B$27</f>
-        <v>1.6443952240485242E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="Z8" s="4">
         <f>Z$5*Calculations!$B$27</f>
-        <v>1.7173790618235372E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="AA8" s="4">
         <f>AA$5*Calculations!$B$27</f>
-        <v>1.6957661324104886E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="AB8" s="4">
         <f>AB$5*Calculations!$B$27</f>
-        <v>1.7045084694976261E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="AC8" s="4">
         <f>AC$5*Calculations!$B$27</f>
-        <v>1.7138495255582494E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="AD8" s="4">
         <f>AD$5*Calculations!$B$27</f>
-        <v>1.7261141230549557E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
       <c r="AE8" s="4">
         <f>AE$5*Calculations!$B$27</f>
-        <v>1.7416141443415431E-3</v>
-      </c>
-      <c r="AG8" s="4"/>
-      <c r="AH8" s="4"/>
+        <v>2.1523608730573507E-4</v>
+      </c>
     </row>
-    <row r="13" spans="1:34">
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AE13" s="23"/>
-      <c r="AF13" s="23"/>
+    <row r="13" spans="1:32">
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="30"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16756,91 +16759,91 @@
         <v>5.7245968727451246E-4</v>
       </c>
       <c r="E12" s="4">
-        <v>5.6525537747016295E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="F12" s="4">
-        <v>5.6816948983254214E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="G12" s="4">
-        <v>5.7128317518608321E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="H12" s="4">
-        <v>5.7537137435165198E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="I12" s="4">
-        <v>5.8053804811384778E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="J12" s="4">
-        <v>5.8402553055494823E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="K12" s="4">
-        <v>5.8760417107298871E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="L12" s="4">
-        <v>5.9096130220580865E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="M12" s="4">
-        <v>5.946019196444121E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="N12" s="4">
-        <v>5.9865845018156332E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="O12" s="4">
-        <v>6.0321943227520944E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="P12" s="4">
-        <v>6.0839429137508894E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Q12" s="4">
-        <v>6.1395089969970801E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="R12" s="4">
-        <v>6.1977379967962927E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="S12" s="4">
-        <v>6.2567088851316315E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="T12" s="4">
-        <v>6.3167004143386532E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="U12" s="4">
-        <v>6.3779136032516399E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="V12" s="4">
-        <v>6.437466870978497E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="W12" s="4">
-        <v>6.4981143154692399E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="X12" s="4">
-        <v>6.5593323238593052E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Y12" s="4">
-        <v>6.6206558943440969E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Z12" s="4">
-        <v>6.6830617483670774E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AA12" s="4">
-        <v>6.7444724581067943E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AB12" s="4">
-        <v>6.8055623616867665E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AC12" s="4">
-        <v>6.8655076394605308E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AD12" s="4">
-        <v>6.9253674881163997E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AE12" s="4">
-        <v>6.9843365885812099E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AF12" s="4">
-        <v>7.0421403083949718E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AG12" s="4">
-        <v>7.0992567085904998E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AH12" s="4"/>
       <c r="AI12" s="4"/>
@@ -16963,94 +16966,94 @@
         <v>5</v>
       </c>
       <c r="D14" s="4">
-        <v>3.8258341226368855E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="E14" s="4">
-        <v>3.0425177990638558E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="F14" s="4">
-        <v>3.1369602145278982E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="G14" s="4">
-        <v>3.1866725580745358E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="H14" s="4">
-        <v>3.2176784865192677E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="I14" s="4">
-        <v>3.2673519826153288E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="J14" s="4">
-        <v>3.3038240919707824E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="K14" s="4">
-        <v>3.3340389823551702E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="L14" s="4">
-        <v>3.3475402773417714E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="M14" s="4">
-        <v>3.3555107094994109E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="N14" s="4">
-        <v>3.3533649804280095E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="O14" s="4">
-        <v>3.3530916094466514E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="P14" s="4">
-        <v>3.3543094523282268E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Q14" s="4">
-        <v>3.3562165718775656E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="R14" s="4">
-        <v>3.3577393040427292E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="S14" s="4">
-        <v>3.3592389782957394E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="T14" s="4">
-        <v>3.3615828155893885E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="U14" s="4">
-        <v>3.3637923107499002E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="V14" s="4">
-        <v>3.3656727929620473E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="W14" s="4">
-        <v>3.3676884833871952E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="X14" s="4">
-        <v>3.3691991114356807E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Y14" s="4">
-        <v>3.3705013729136348E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Z14" s="4">
-        <v>3.3713686099786852E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AA14" s="4">
-        <v>3.3722694633495147E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AB14" s="4">
-        <v>3.3729739602263772E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AC14" s="4">
-        <v>3.3742953237129352E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AD14" s="4">
-        <v>3.3751721202413692E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AE14" s="4">
-        <v>3.3760101841942016E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AF14" s="4">
-        <v>3.3764787130259203E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AG14" s="4">
-        <v>3.3772719520374359E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AH14" s="4"/>
       <c r="AI14" s="4"/>
@@ -17068,94 +17071,94 @@
         <v>2</v>
       </c>
       <c r="D15" s="4">
-        <v>1.2294220931562134E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="E15" s="4">
-        <v>9.7770537903301043E-4</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="F15" s="4">
-        <v>1.0080542097404184E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="G15" s="4">
-        <v>1.0240291452707345E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="H15" s="4">
-        <v>1.0339928217467291E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="I15" s="4">
-        <v>1.049955273747318E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="J15" s="4">
-        <v>1.0616754935969699E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="K15" s="4">
-        <v>1.0713849719983116E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="L15" s="4">
-        <v>1.0757235789035442E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="M15" s="4">
-        <v>1.0782848570647235E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="N15" s="4">
-        <v>1.0775953324691067E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="O15" s="4">
-        <v>1.0775074853975044E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="P15" s="4">
-        <v>1.0778988361191009E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Q15" s="4">
-        <v>1.0785116841499065E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="R15" s="4">
-        <v>1.0790010102695979E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="S15" s="4">
-        <v>1.0794829267876918E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="T15" s="4">
-        <v>1.0802361129581342E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="U15" s="4">
-        <v>1.0809461286247785E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="V15" s="4">
-        <v>1.0815504168148291E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="W15" s="4">
-        <v>1.0821981538212447E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="X15" s="4">
-        <v>1.0826835903137368E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Y15" s="4">
-        <v>1.0831020687371974E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="Z15" s="4">
-        <v>1.0833807531687749E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AA15" s="4">
-        <v>1.0836702401149649E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AB15" s="4">
-        <v>1.0838966283997708E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AC15" s="4">
-        <v>1.0843212452052544E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AD15" s="4">
-        <v>1.0846030015461477E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AE15" s="4">
-        <v>1.0848723112720957E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AF15" s="4">
-        <v>1.0850228718239992E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AG15" s="4">
-        <v>1.0852777771687293E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="AH15" s="4"/>
       <c r="AI15" s="4"/>
@@ -18567,16 +18570,16 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>1.232672246515414E-3</v>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="C5">
-        <v>4.2170366328158899E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="D5">
-        <v>4.2170366328158899E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="E5">
-        <v>4.2170366328158899E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -18585,7 +18588,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>1.2651109898447668E-3</v>
+        <v>2.1523608730573507E-4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -19216,7 +19219,7 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="40" max="40" width="8.7109375" style="26"/>
+    <col min="40" max="40" width="8.7109375" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72">
@@ -19331,7 +19334,7 @@
       <c r="AM1">
         <v>2019</v>
       </c>
-      <c r="AN1" s="27">
+      <c r="AN1" s="25">
         <v>2020</v>
       </c>
       <c r="AO1">
@@ -19508,7 +19511,7 @@
         <f t="shared" si="0"/>
         <v>3.4824495702621549E-4</v>
       </c>
-      <c r="AN2" s="28">
+      <c r="AN2" s="26">
         <f t="shared" si="0"/>
         <v>3.5107788164238408E-4</v>
       </c>
@@ -19718,7 +19721,7 @@
         <f t="array" ref="AM3">TREND($AO$3:$AS$3,$AO$1:$AS$1,AM1)</f>
         <v>1.0444155998202975E-4</v>
       </c>
-      <c r="AN3" s="28" cm="1">
+      <c r="AN3" s="26" cm="1">
         <f t="array" ref="AN3">TREND($AO$3:$AS$3,$AO$1:$AS$1,AN1)</f>
         <v>1.0688599085026222E-4</v>
       </c>
@@ -19973,7 +19976,7 @@
         <f>AM5/AN5*AN4</f>
         <v>1.1237863961245848E-3</v>
       </c>
-      <c r="AN4" s="29">
+      <c r="AN4" s="27">
         <f>AN5/AO5*AO4</f>
         <v>1.1204363366810234E-3</v>
       </c>
@@ -20156,7 +20159,7 @@
         <f>V5</f>
         <v>7.8040477200267344E-4</v>
       </c>
-      <c r="V5" s="25">
+      <c r="V5" s="23">
         <f>Calculations!B22</f>
         <v>7.8040477200267344E-4</v>
       </c>
@@ -20228,7 +20231,7 @@
         <f t="shared" si="3"/>
         <v>7.4276317604295334E-4</v>
       </c>
-      <c r="AN5" s="28">
+      <c r="AN5" s="26">
         <f t="shared" si="3"/>
         <v>7.4054896451591099E-4</v>
       </c>
@@ -20377,103 +20380,103 @@
       <c r="O6" s="9"/>
       <c r="P6" s="4">
         <f>TREND($AO6:$BR6,$AO$1:$BR$1,P$1)</f>
-        <v>4.236427364823752E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" ref="Q6:AN6" si="4">TREND($AO6:$BR6,$AO$1:$BR$1,Q$1)</f>
-        <v>4.2882977835183994E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="R6" s="4">
         <f t="shared" si="4"/>
-        <v>4.3401682022130295E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="S6" s="4">
         <f t="shared" si="4"/>
-        <v>4.3920386209076769E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="T6" s="4">
         <f t="shared" si="4"/>
-        <v>4.4439090396023069E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="U6" s="4">
         <f t="shared" si="4"/>
-        <v>4.4957794582969543E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="4"/>
-        <v>4.5476498769915844E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="W6" s="4">
         <f t="shared" si="4"/>
-        <v>4.5995202956862317E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="X6" s="4">
         <f t="shared" si="4"/>
-        <v>4.6513907143808618E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Y6" s="4">
         <f t="shared" si="4"/>
-        <v>4.7032611330755092E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="Z6" s="4">
         <f t="shared" si="4"/>
-        <v>4.7551315517701392E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AA6" s="4">
         <f t="shared" si="4"/>
-        <v>4.8070019704647866E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AB6" s="4">
         <f t="shared" si="4"/>
-        <v>4.8588723891594167E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AC6" s="4">
         <f t="shared" si="4"/>
-        <v>4.9107428078540641E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AD6" s="4">
         <f t="shared" si="4"/>
-        <v>4.9626132265486941E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="4"/>
-        <v>5.0144836452433242E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="4"/>
-        <v>5.0663540639379716E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="4"/>
-        <v>5.1182244826326016E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="4"/>
-        <v>5.170094901327249E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="4"/>
-        <v>5.2219653200218791E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AJ6" s="4">
         <f t="shared" si="4"/>
-        <v>5.2738357387165265E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AK6" s="4">
         <f t="shared" si="4"/>
-        <v>5.3257061574111565E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="4"/>
-        <v>5.3775765761058039E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AM6" s="4">
         <f t="shared" si="4"/>
-        <v>5.429446994800434E-4</v>
-      </c>
-      <c r="AN6" s="28">
+        <v>5.7245968727451246E-4</v>
+      </c>
+      <c r="AN6" s="26">
         <f t="shared" si="4"/>
-        <v>5.4813174134950814E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AO6" s="10">
         <f>BNVFE!D12</f>
@@ -20481,119 +20484,119 @@
       </c>
       <c r="AP6" s="10">
         <f>BNVFE!E12</f>
-        <v>5.6525537747016295E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AQ6" s="10">
         <f>BNVFE!F12</f>
-        <v>5.6816948983254214E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AR6" s="10">
         <f>BNVFE!G12</f>
-        <v>5.7128317518608321E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AS6" s="10">
         <f>BNVFE!H12</f>
-        <v>5.7537137435165198E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AT6" s="10">
         <f>BNVFE!I12</f>
-        <v>5.8053804811384778E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AU6" s="10">
         <f>BNVFE!J12</f>
-        <v>5.8402553055494823E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AV6" s="10">
         <f>BNVFE!K12</f>
-        <v>5.8760417107298871E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AW6" s="10">
         <f>BNVFE!L12</f>
-        <v>5.9096130220580865E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AX6" s="10">
         <f>BNVFE!M12</f>
-        <v>5.946019196444121E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AY6" s="10">
         <f>BNVFE!N12</f>
-        <v>5.9865845018156332E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="AZ6" s="10">
         <f>BNVFE!O12</f>
-        <v>6.0321943227520944E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BA6" s="10">
         <f>BNVFE!P12</f>
-        <v>6.0839429137508894E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BB6" s="10">
         <f>BNVFE!Q12</f>
-        <v>6.1395089969970801E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BC6" s="10">
         <f>BNVFE!R12</f>
-        <v>6.1977379967962927E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BD6" s="10">
         <f>BNVFE!S12</f>
-        <v>6.2567088851316315E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BE6" s="10">
         <f>BNVFE!T12</f>
-        <v>6.3167004143386532E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BF6" s="10">
         <f>BNVFE!U12</f>
-        <v>6.3779136032516399E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BG6" s="10">
         <f>BNVFE!V12</f>
-        <v>6.437466870978497E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BH6" s="10">
         <f>BNVFE!W12</f>
-        <v>6.4981143154692399E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BI6" s="10">
         <f>BNVFE!X12</f>
-        <v>6.5593323238593052E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BJ6" s="10">
         <f>BNVFE!Y12</f>
-        <v>6.6206558943440969E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BK6" s="10">
         <f>BNVFE!Z12</f>
-        <v>6.6830617483670774E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BL6" s="10">
         <f>BNVFE!AA12</f>
-        <v>6.7444724581067943E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BM6" s="10">
         <f>BNVFE!AB12</f>
-        <v>6.8055623616867665E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BN6" s="10">
         <f>BNVFE!AC12</f>
-        <v>6.8655076394605308E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BO6" s="10">
         <f>BNVFE!AD12</f>
-        <v>6.9253674881163997E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BP6" s="10">
         <f>BNVFE!AE12</f>
-        <v>6.9843365885812099E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BQ6" s="10">
         <f>BNVFE!AF12</f>
-        <v>7.0421403083949718E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BR6" s="10">
         <f>BNVFE!AG12</f>
-        <v>7.0992567085904998E-4</v>
+        <v>5.7245968727451246E-4</v>
       </c>
       <c r="BS6" s="10"/>
       <c r="BT6" s="4"/>
@@ -20714,7 +20717,7 @@
         <f t="shared" si="5"/>
         <v>4.6159076773102222E-5</v>
       </c>
-      <c r="AN7" s="28">
+      <c r="AN7" s="26">
         <f t="shared" si="5"/>
         <v>4.6599105683549815E-5</v>
       </c>
@@ -20852,264 +20855,264 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="4">
-        <f>TREND($AO8:$AT8,$AO$1:$AT$1,F$1)</f>
-        <v>5.6550914138770239E-4</v>
+        <f>SYFAFE!$E$5</f>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" ref="G8:AN9" si="6">TREND($AO8:$AT8,$AO$1:$AT$1,G$1)</f>
-        <v>5.5917423769000218E-4</v>
+        <f>F8</f>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="6"/>
-        <v>5.5283933399230198E-4</v>
+        <f t="shared" ref="H8:BR8" si="6">G8</f>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="6"/>
-        <v>5.4650443029460177E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="6"/>
-        <v>5.401695265969033E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="K8" s="4">
         <f t="shared" si="6"/>
-        <v>5.338346228992031E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="L8" s="4">
         <f t="shared" si="6"/>
-        <v>5.2749971920150289E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="6"/>
-        <v>5.2116481550380268E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="6"/>
-        <v>5.1482991180610421E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="O8" s="4">
         <f t="shared" si="6"/>
-        <v>5.0849500810840401E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="6"/>
-        <v>5.021601044107038E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Q8" s="4">
         <f t="shared" si="6"/>
-        <v>4.9582520071300533E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="R8" s="4">
         <f t="shared" si="6"/>
-        <v>4.8949029701530512E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="S8" s="4">
         <f t="shared" si="6"/>
-        <v>4.8315539331760492E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="T8" s="4">
         <f t="shared" si="6"/>
-        <v>4.7682048961990471E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="U8" s="4">
         <f t="shared" si="6"/>
-        <v>4.7048558592220624E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="V8" s="4">
         <f t="shared" si="6"/>
-        <v>4.6415068222450603E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="W8" s="4">
         <f t="shared" si="6"/>
-        <v>4.5781577852680583E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="X8" s="4">
         <f t="shared" si="6"/>
-        <v>4.5148087482910562E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Y8" s="4">
         <f t="shared" si="6"/>
-        <v>4.4514597113140715E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="Z8" s="4">
         <f t="shared" si="6"/>
-        <v>4.3881106743370694E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AA8" s="4">
         <f t="shared" si="6"/>
-        <v>4.3247616373600674E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AB8" s="4">
         <f t="shared" si="6"/>
-        <v>4.2614126003830653E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AC8" s="4">
         <f t="shared" si="6"/>
-        <v>4.1980635634060806E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AD8" s="4">
         <f t="shared" si="6"/>
-        <v>4.1347145264290786E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="6"/>
-        <v>4.0713654894520765E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AF8" s="4">
         <f t="shared" si="6"/>
-        <v>4.0080164524750744E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="6"/>
-        <v>3.9446674154980897E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AH8" s="4">
         <f t="shared" si="6"/>
-        <v>3.8813183785210877E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AI8" s="4">
         <f t="shared" si="6"/>
-        <v>3.8179693415440856E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AJ8" s="4">
         <f t="shared" si="6"/>
-        <v>3.7546203045671009E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AK8" s="4">
         <f t="shared" si="6"/>
-        <v>3.6912712675900988E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AL8" s="4">
         <f t="shared" si="6"/>
-        <v>3.6279222306130968E-4</v>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="AM8" s="4">
         <f t="shared" si="6"/>
-        <v>3.5645731936360947E-4</v>
-      </c>
-      <c r="AN8" s="28">
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AN8" s="4">
         <f t="shared" si="6"/>
-        <v>3.50122415665911E-4</v>
-      </c>
-      <c r="AO8" s="10">
-        <f>BNVFE!D14</f>
-        <v>3.8258341226368855E-4</v>
-      </c>
-      <c r="AP8" s="10">
-        <f>BNVFE!E14</f>
-        <v>3.0425177990638558E-4</v>
-      </c>
-      <c r="AQ8" s="10">
-        <f>BNVFE!F14</f>
-        <v>3.1369602145278982E-4</v>
-      </c>
-      <c r="AR8" s="10">
-        <f>BNVFE!G14</f>
-        <v>3.1866725580745358E-4</v>
-      </c>
-      <c r="AS8" s="10">
-        <f>BNVFE!H14</f>
-        <v>3.2176784865192677E-4</v>
-      </c>
-      <c r="AT8" s="10">
-        <f>BNVFE!I14</f>
-        <v>3.2673519826153288E-4</v>
-      </c>
-      <c r="AU8" s="10">
-        <f>BNVFE!J14</f>
-        <v>3.3038240919707824E-4</v>
-      </c>
-      <c r="AV8" s="10">
-        <f>BNVFE!K14</f>
-        <v>3.3340389823551702E-4</v>
-      </c>
-      <c r="AW8" s="10">
-        <f>BNVFE!L14</f>
-        <v>3.3475402773417714E-4</v>
-      </c>
-      <c r="AX8" s="10">
-        <f>BNVFE!M14</f>
-        <v>3.3555107094994109E-4</v>
-      </c>
-      <c r="AY8" s="10">
-        <f>BNVFE!N14</f>
-        <v>3.3533649804280095E-4</v>
-      </c>
-      <c r="AZ8" s="10">
-        <f>BNVFE!O14</f>
-        <v>3.3530916094466514E-4</v>
-      </c>
-      <c r="BA8" s="10">
-        <f>BNVFE!P14</f>
-        <v>3.3543094523282268E-4</v>
-      </c>
-      <c r="BB8" s="10">
-        <f>BNVFE!Q14</f>
-        <v>3.3562165718775656E-4</v>
-      </c>
-      <c r="BC8" s="10">
-        <f>BNVFE!R14</f>
-        <v>3.3577393040427292E-4</v>
-      </c>
-      <c r="BD8" s="10">
-        <f>BNVFE!S14</f>
-        <v>3.3592389782957394E-4</v>
-      </c>
-      <c r="BE8" s="10">
-        <f>BNVFE!T14</f>
-        <v>3.3615828155893885E-4</v>
-      </c>
-      <c r="BF8" s="10">
-        <f>BNVFE!U14</f>
-        <v>3.3637923107499002E-4</v>
-      </c>
-      <c r="BG8" s="10">
-        <f>BNVFE!V14</f>
-        <v>3.3656727929620473E-4</v>
-      </c>
-      <c r="BH8" s="10">
-        <f>BNVFE!W14</f>
-        <v>3.3676884833871952E-4</v>
-      </c>
-      <c r="BI8" s="10">
-        <f>BNVFE!X14</f>
-        <v>3.3691991114356807E-4</v>
-      </c>
-      <c r="BJ8" s="10">
-        <f>BNVFE!Y14</f>
-        <v>3.3705013729136348E-4</v>
-      </c>
-      <c r="BK8" s="10">
-        <f>BNVFE!Z14</f>
-        <v>3.3713686099786852E-4</v>
-      </c>
-      <c r="BL8" s="10">
-        <f>BNVFE!AA14</f>
-        <v>3.3722694633495147E-4</v>
-      </c>
-      <c r="BM8" s="10">
-        <f>BNVFE!AB14</f>
-        <v>3.3729739602263772E-4</v>
-      </c>
-      <c r="BN8" s="10">
-        <f>BNVFE!AC14</f>
-        <v>3.3742953237129352E-4</v>
-      </c>
-      <c r="BO8" s="10">
-        <f>BNVFE!AD14</f>
-        <v>3.3751721202413692E-4</v>
-      </c>
-      <c r="BP8" s="10">
-        <f>BNVFE!AE14</f>
-        <v>3.3760101841942016E-4</v>
-      </c>
-      <c r="BQ8" s="10">
-        <f>BNVFE!AF14</f>
-        <v>3.3764787130259203E-4</v>
-      </c>
-      <c r="BR8" s="10">
-        <f>BNVFE!AG14</f>
-        <v>3.3772719520374359E-4</v>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AO8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AP8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AQ8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AR8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AS8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AT8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AU8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AV8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AW8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AX8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AY8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="AZ8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BA8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BB8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BC8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BD8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BE8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BF8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BG8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BH8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BI8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BJ8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BK8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BL8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BM8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BN8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BO8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BP8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BQ8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
+      </c>
+      <c r="BR8" s="4">
+        <f t="shared" si="6"/>
+        <v>7.1745362435245036E-5</v>
       </c>
       <c r="BS8" s="10"/>
       <c r="BT8" s="4"/>
@@ -21125,264 +21128,264 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="19">
-        <f>TREND($AO9:$AT9,$AO$1:$AT$1,F$1)</f>
-        <v>1.817249284777292E-3</v>
-      </c>
-      <c r="G9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.7968922323952086E-3</v>
-      </c>
-      <c r="H9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.7765351800131182E-3</v>
-      </c>
-      <c r="I9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.7561781276310348E-3</v>
-      </c>
-      <c r="J9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.7358210752489514E-3</v>
-      </c>
-      <c r="K9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.7154640228668611E-3</v>
-      </c>
-      <c r="L9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.6951069704847777E-3</v>
-      </c>
-      <c r="M9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.6747499181026873E-3</v>
-      </c>
-      <c r="N9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.6543928657206039E-3</v>
-      </c>
-      <c r="O9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.6340358133385205E-3</v>
-      </c>
-      <c r="P9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.6136787609564301E-3</v>
-      </c>
-      <c r="Q9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.5933217085743467E-3</v>
-      </c>
-      <c r="R9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.5729646561922633E-3</v>
-      </c>
-      <c r="S9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.552607603810173E-3</v>
-      </c>
-      <c r="T9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.5322505514280896E-3</v>
-      </c>
-      <c r="U9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.5118934990460062E-3</v>
-      </c>
-      <c r="V9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.4915364466639158E-3</v>
-      </c>
-      <c r="W9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.4711793942818324E-3</v>
-      </c>
-      <c r="X9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.450822341899749E-3</v>
-      </c>
-      <c r="Y9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.4304652895176587E-3</v>
-      </c>
-      <c r="Z9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.4101082371355753E-3</v>
-      </c>
-      <c r="AA9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.3897511847534849E-3</v>
-      </c>
-      <c r="AB9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.3693941323714015E-3</v>
-      </c>
-      <c r="AC9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.3490370799893181E-3</v>
-      </c>
-      <c r="AD9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.3286800276072278E-3</v>
-      </c>
-      <c r="AE9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.3083229752251443E-3</v>
-      </c>
-      <c r="AF9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.2879659228430609E-3</v>
-      </c>
-      <c r="AG9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.2676088704609706E-3</v>
-      </c>
-      <c r="AH9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.2472518180788872E-3</v>
-      </c>
-      <c r="AI9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.2268947656968038E-3</v>
-      </c>
-      <c r="AJ9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.2065377133147134E-3</v>
-      </c>
-      <c r="AK9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.18618066093263E-3</v>
-      </c>
-      <c r="AL9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.1658236085505466E-3</v>
-      </c>
-      <c r="AM9" s="19">
-        <f t="shared" si="6"/>
-        <v>1.1454665561684563E-3</v>
-      </c>
-      <c r="AN9" s="29">
-        <f t="shared" si="6"/>
-        <v>1.1251095037863729E-3</v>
-      </c>
-      <c r="AO9" s="10">
-        <f>BNVFE!D15</f>
-        <v>1.2294220931562134E-3</v>
-      </c>
-      <c r="AP9" s="10">
-        <f>BNVFE!E15</f>
-        <v>9.7770537903301043E-4</v>
-      </c>
-      <c r="AQ9" s="10">
-        <f>BNVFE!F15</f>
-        <v>1.0080542097404184E-3</v>
-      </c>
-      <c r="AR9" s="10">
-        <f>BNVFE!G15</f>
-        <v>1.0240291452707345E-3</v>
-      </c>
-      <c r="AS9" s="10">
-        <f>BNVFE!H15</f>
-        <v>1.0339928217467291E-3</v>
-      </c>
-      <c r="AT9" s="10">
-        <f>BNVFE!I15</f>
-        <v>1.049955273747318E-3</v>
-      </c>
-      <c r="AU9" s="10">
-        <f>BNVFE!J15</f>
-        <v>1.0616754935969699E-3</v>
-      </c>
-      <c r="AV9" s="10">
-        <f>BNVFE!K15</f>
-        <v>1.0713849719983116E-3</v>
-      </c>
-      <c r="AW9" s="10">
-        <f>BNVFE!L15</f>
-        <v>1.0757235789035442E-3</v>
-      </c>
-      <c r="AX9" s="10">
-        <f>BNVFE!M15</f>
-        <v>1.0782848570647235E-3</v>
-      </c>
-      <c r="AY9" s="10">
-        <f>BNVFE!N15</f>
-        <v>1.0775953324691067E-3</v>
-      </c>
-      <c r="AZ9" s="10">
-        <f>BNVFE!O15</f>
-        <v>1.0775074853975044E-3</v>
-      </c>
-      <c r="BA9" s="10">
-        <f>BNVFE!P15</f>
-        <v>1.0778988361191009E-3</v>
-      </c>
-      <c r="BB9" s="10">
-        <f>BNVFE!Q15</f>
-        <v>1.0785116841499065E-3</v>
-      </c>
-      <c r="BC9" s="10">
-        <f>BNVFE!R15</f>
-        <v>1.0790010102695979E-3</v>
-      </c>
-      <c r="BD9" s="10">
-        <f>BNVFE!S15</f>
-        <v>1.0794829267876918E-3</v>
-      </c>
-      <c r="BE9" s="10">
-        <f>BNVFE!T15</f>
-        <v>1.0802361129581342E-3</v>
-      </c>
-      <c r="BF9" s="10">
-        <f>BNVFE!U15</f>
-        <v>1.0809461286247785E-3</v>
-      </c>
-      <c r="BG9" s="10">
-        <f>BNVFE!V15</f>
-        <v>1.0815504168148291E-3</v>
-      </c>
-      <c r="BH9" s="10">
-        <f>BNVFE!W15</f>
-        <v>1.0821981538212447E-3</v>
-      </c>
-      <c r="BI9" s="10">
-        <f>BNVFE!X15</f>
-        <v>1.0826835903137368E-3</v>
-      </c>
-      <c r="BJ9" s="10">
-        <f>BNVFE!Y15</f>
-        <v>1.0831020687371974E-3</v>
-      </c>
-      <c r="BK9" s="10">
-        <f>BNVFE!Z15</f>
-        <v>1.0833807531687749E-3</v>
-      </c>
-      <c r="BL9" s="10">
-        <f>BNVFE!AA15</f>
-        <v>1.0836702401149649E-3</v>
-      </c>
-      <c r="BM9" s="10">
-        <f>BNVFE!AB15</f>
-        <v>1.0838966283997708E-3</v>
-      </c>
-      <c r="BN9" s="10">
-        <f>BNVFE!AC15</f>
-        <v>1.0843212452052544E-3</v>
-      </c>
-      <c r="BO9" s="10">
-        <f>BNVFE!AD15</f>
-        <v>1.0846030015461477E-3</v>
-      </c>
-      <c r="BP9" s="10">
-        <f>BNVFE!AE15</f>
-        <v>1.0848723112720957E-3</v>
-      </c>
-      <c r="BQ9" s="10">
-        <f>BNVFE!AF15</f>
-        <v>1.0850228718239992E-3</v>
-      </c>
-      <c r="BR9" s="10">
-        <f>BNVFE!AG15</f>
-        <v>1.0852777771687293E-3</v>
+        <f>SYFAFE!$B$5</f>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="G9" s="4">
+        <f>F9</f>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" ref="H9:BR9" si="7">G9</f>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="J9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="O9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="Q9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="R9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="S9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="T9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="U9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="V9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="W9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="X9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="Y9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AA9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AB9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AC9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AD9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AE9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AF9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AG9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AH9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AI9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AJ9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AK9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AL9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AM9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AN9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AO9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AP9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AQ9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AR9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AS9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AT9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AU9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AV9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AW9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AX9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AY9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="AZ9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BA9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BB9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BC9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BD9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BE9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BF9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BG9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BH9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BI9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BJ9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BK9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BL9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BM9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BN9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BO9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BP9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BQ9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
+      </c>
+      <c r="BR9" s="4">
+        <f t="shared" si="7"/>
+        <v>7.5686214263268839E-4</v>
       </c>
       <c r="BS9" s="10"/>
       <c r="BT9" s="4"/>
@@ -21402,139 +21405,139 @@
         <v>3.2890937975528366E-3</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" ref="G10:AN13" si="7">TREND($AO10:$BR10,$AO$1:$BR$1,G$1)</f>
+        <f t="shared" ref="G10:AN13" si="8">TREND($AO10:$BR10,$AO$1:$BR$1,G$1)</f>
         <v>3.2917330420467188E-3</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.294372286540601E-3</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2970115310344832E-3</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.2996507755283645E-3</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3022900200222467E-3</v>
       </c>
       <c r="L10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3049292645161289E-3</v>
       </c>
       <c r="M10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3075685090100111E-3</v>
       </c>
       <c r="N10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3102077535038933E-3</v>
       </c>
       <c r="O10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3128469979977755E-3</v>
       </c>
       <c r="P10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3154862424916577E-3</v>
       </c>
       <c r="Q10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.318125486985539E-3</v>
       </c>
       <c r="R10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3207647314794212E-3</v>
       </c>
       <c r="S10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3234039759733034E-3</v>
       </c>
       <c r="T10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3260432204671856E-3</v>
       </c>
       <c r="U10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3286824649610678E-3</v>
       </c>
       <c r="V10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.33132170945495E-3</v>
       </c>
       <c r="W10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3339609539488322E-3</v>
       </c>
       <c r="X10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3366001984427144E-3</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3392394429365957E-3</v>
       </c>
       <c r="Z10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3418786874304779E-3</v>
       </c>
       <c r="AA10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3445179319243601E-3</v>
       </c>
       <c r="AB10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3471571764182423E-3</v>
       </c>
       <c r="AC10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3497964209121245E-3</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3524356654060067E-3</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3550749098998889E-3</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3577141543937711E-3</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3603533988876525E-3</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3629926433815347E-3</v>
       </c>
       <c r="AI10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3656318878754169E-3</v>
       </c>
       <c r="AJ10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3682711323692991E-3</v>
       </c>
       <c r="AK10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3709103768631813E-3</v>
       </c>
       <c r="AL10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3735496213570635E-3</v>
       </c>
       <c r="AM10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>3.3761888658509456E-3</v>
       </c>
-      <c r="AN10" s="28">
-        <f t="shared" si="7"/>
+      <c r="AN10" s="26">
+        <f t="shared" si="8"/>
         <v>3.3788281103448278E-3</v>
       </c>
       <c r="AO10" s="10">
@@ -21676,135 +21679,135 @@
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="I11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="L11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="M11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="N11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="O11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="P11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="Q11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="R11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="S11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="T11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="U11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="V11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="W11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="X11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="Y11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="Z11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AA11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AB11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AC11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AD11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AE11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AF11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AG11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AH11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AI11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AJ11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AK11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AL11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AM11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
-      <c r="AN11" s="28">
-        <f t="shared" si="7"/>
+      <c r="AN11" s="26">
+        <f t="shared" si="8"/>
         <v>1.2594546332724645E-5</v>
       </c>
       <c r="AO11" s="10">
@@ -21946,135 +21949,135 @@
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="I12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="J12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="L12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="M12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="N12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="O12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="P12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="S12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="T12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="V12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="W12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="X12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="Y12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="Z12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AA12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AB12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AC12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AD12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AE12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AF12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AG12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AH12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AI12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AJ12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AM12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
-      <c r="AN12" s="28">
-        <f t="shared" si="7"/>
+      <c r="AN12" s="26">
+        <f t="shared" si="8"/>
         <v>5.2454271866069317E-3</v>
       </c>
       <c r="AO12" s="10">
@@ -22232,71 +22235,71 @@
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="X13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="Y13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AA13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AB13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AD13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AE13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AF13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AG13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AJ13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AL13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AM13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
-      <c r="AN13" s="28">
-        <f t="shared" si="7"/>
+      <c r="AN13" s="26">
+        <f t="shared" si="8"/>
         <v>1.4345302324303025E-3</v>
       </c>
       <c r="AO13" s="10">
@@ -22450,74 +22453,74 @@
       <c r="U14" s="9"/>
       <c r="V14" s="9"/>
       <c r="W14">
-        <f t="shared" ref="W14:AM14" si="8">$AO14</f>
+        <f t="shared" ref="W14:AM14" si="9">$AO14</f>
         <v>0</v>
       </c>
       <c r="X14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AK14" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL14" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM14" s="20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AN14" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="28">
         <f>$AO14</f>
         <v>0</v>
       </c>
@@ -22644,10 +22647,10 @@
       <c r="BS14" s="11"/>
     </row>
     <row r="15" spans="1:72">
-      <c r="E15" s="24"/>
+      <c r="E15" s="22"/>
       <c r="X15" s="4"/>
       <c r="AH15" s="4"/>
-      <c r="AN15" s="27"/>
+      <c r="AN15" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
